--- a/extenbooks/S204_extenbook.xlsx
+++ b/extenbooks/S204_extenbook.xlsx
@@ -10941,7 +10941,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -11803,11 +11803,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11830,64 +11830,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ayres (1939) Index 1831-1866 (monthly)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S204_research.json", "adequacy_report": "Technical/docs/chapters/CH2_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S204_DPR.md", "epr": "Technical/docs/series/S204_EPR.md", "loader": "Technical/code/L01_loaders/L01_S204_load.py", "processor": "Technical/code/P02_processors/P02_S204_construct.py", "validator": "Technical/code/V03_validators/V03_S204_validate.py", "processed": "Technical/data/processed/S204.parquet", "chopped_csv": "Technical/chopped/S204.csv", "extenbook_xlsx": "Technical/extenbooks/S204_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S204_extenbook.xlsx
+++ b/extenbooks/S204_extenbook.xlsx
@@ -11030,7 +11030,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>In Shaikh (2016) the series appears as **Figure 2.4A** in Chapter 2 ("The Wealth of Nations: A Long View").</t>
+          <t>In Shaikh (2016) the series appears as **Figure 2.4A** in Chapter 2 ("Turbulent Trends and Hidden Structures").</t>
         </is>
       </c>
     </row>
@@ -11788,7 +11788,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-18T23:18:12.116895+00:00</t>
+          <t>2026-07-02T06:20:56.965511+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S204_extenbook.xlsx
+++ b/extenbooks/S204_extenbook.xlsx
@@ -11788,7 +11788,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-02T06:20:56.965511+00:00</t>
+          <t>2026-07-11T03:44:24.113997+00:00</t>
         </is>
       </c>
     </row>
@@ -11803,11 +11803,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11830,6 +11830,114 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Reconstructs Shaikh (2016) Ch.2 figure; book_period_validated; real data present in chopped CSV; KB-verified.", "date": "2026-06-10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>percent_deviation_from_trend</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
